--- a/automation-agency/demo/testdata_ror_as.xlsx
+++ b/automation-agency/demo/testdata_ror_as.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -606,12 +606,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lonn vikar</t>
+          <t>Lønn vikar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lonn assistent</t>
+          <t>Lønn assistent</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -696,12 +696,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sikkerhetsutsstyr</t>
+          <t>Sikkerhetsutstyr</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Verktoy</t>
+          <t>Verktøy</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -756,7 +756,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avlopsdeler</t>
+          <t>Avløpsdeler</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -936,12 +936,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lonn larling uke 3-4</t>
+          <t>Lønn lærling uke 3-4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lonn assistent</t>
+          <t>Lønn assistent</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -996,12 +996,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sikkerhetsutsstyr</t>
+          <t>Sikkerhetsutstyr</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Verktoy</t>
+          <t>Verktøy</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lonn larlingsassistent uke 1-2</t>
+          <t>Lønn lærlingassistent uke 1-2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lonn assistent</t>
+          <t>Lønn assistent</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Avlopsdeler</t>
+          <t>Avløpsdeler</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Utskifting av vannror kjokken</t>
+          <t>Utskifting av vannrør kjøkken</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arsavtale vedlikehold</t>
+          <t>Årsavtale vedlikehold</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lonn assistent</t>
+          <t>Lønn assistent</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nytt boreverktoy</t>
+          <t>Nytt boreverktøy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Verktoy</t>
+          <t>Verktøy</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Verktoy</t>
+          <t>Verktøy</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sikkerhetsutsstyr</t>
+          <t>Sikkerhetsutstyr</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Verktoy</t>
+          <t>Verktøy</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Akutt rorbrudd natt</t>
+          <t>Akutt rørbrudd natt</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lonn larlingsassistent uke 1-2</t>
+          <t>Lønn lærlingassistent uke 1-2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lonn assistent</t>
+          <t>Lønn assistent</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Akutt rorbrudd natt</t>
+          <t>Akutt rørbrudd natt</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Utskifting av vannror kjokken</t>
+          <t>Utskifting av vannrør kjøkken</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nytt boreverktoy</t>
+          <t>Nytt boreverktøy</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Verktoy</t>
+          <t>Verktøy</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sikkerhetsutsstyr</t>
+          <t>Sikkerhetsutstyr</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Verktoy</t>
+          <t>Verktøy</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Nytt boreverktoy</t>
+          <t>Nytt boreverktøy</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Verktoy</t>
+          <t>Verktøy</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Hasteoppdrag oversvommet kjeller</t>
+          <t>Hasteoppdrag oversvømt kjeller</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Arsavtale vedlikehold</t>
+          <t>Årsavtale vedlikehold</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Hasteoppdrag oversvommet kjeller</t>
+          <t>Hasteoppdrag oversvømt kjeller</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Arsservice varmeanlegg</t>
+          <t>Årsservice varmeanlegg</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Utskifting av vannror kjokken</t>
+          <t>Utskifting av vannrør kjøkken</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rorleggerarbeid</t>
+          <t>Rørleggerarbeid</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Avlopsdeler</t>
+          <t>Avløpsdeler</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
